--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="33">
   <si>
     <t>Дата</t>
   </si>
@@ -53,12 +53,6 @@
   </si>
   <si>
     <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
-    <t>2026-05-11</t>
   </si>
   <si>
     <t>1158</t>
@@ -125,8 +119,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -212,11 +207,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -224,9 +220,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -580,20 +576,20 @@
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
+      <c r="A2" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
       </c>
       <c r="F2">
         <v>16.34</v>
@@ -611,7 +607,7 @@
         <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -621,20 +617,20 @@
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
+      <c r="A3" s="2">
+        <v>46150</v>
+      </c>
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>41.036</v>
@@ -652,7 +648,7 @@
         <v>34.06</v>
       </c>
       <c r="K3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -662,20 +658,20 @@
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" t="s">
+      <c r="A4" s="2">
+        <v>46153</v>
+      </c>
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>53.838</v>
@@ -693,133 +689,133 @@
         <v>109.83</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="D8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="3" t="s">
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="6">
+        <v>53.838</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6">
+        <v>2.0099</v>
+      </c>
+      <c r="E9" s="6">
+        <v>108.21</v>
+      </c>
+      <c r="F9" s="6">
+        <v>109.83</v>
+      </c>
+      <c r="G9" s="6">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="6">
+        <v>41.036</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6">
+        <v>0.82</v>
+      </c>
+      <c r="E10" s="6">
+        <v>33.65</v>
+      </c>
+      <c r="F10" s="6">
+        <v>34.06</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="6">
+        <v>16.34</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="E11" s="6">
+        <v>24.51</v>
+      </c>
+      <c r="F11" s="6">
+        <v>25</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="5">
-        <v>53.838</v>
-      </c>
-      <c r="C9" s="5">
-        <v>1</v>
-      </c>
-      <c r="D9" s="5">
-        <v>2.0099</v>
-      </c>
-      <c r="E9" s="5">
-        <v>108.21</v>
-      </c>
-      <c r="F9" s="5">
-        <v>109.83</v>
-      </c>
-      <c r="G9" s="5">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="5">
-        <v>41.036</v>
-      </c>
-      <c r="C10" s="5">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5">
-        <v>0.82</v>
-      </c>
-      <c r="E10" s="5">
-        <v>33.65</v>
-      </c>
-      <c r="F10" s="5">
-        <v>34.06</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="5">
-        <v>16.34</v>
-      </c>
-      <c r="C11" s="5">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5">
-        <v>1.5</v>
-      </c>
-      <c r="E11" s="5">
-        <v>24.51</v>
-      </c>
-      <c r="F11" s="5">
-        <v>25</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="7">
+      <c r="B12" s="8">
         <v>111.214</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <v>3</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7">
+      <c r="D12" s="8"/>
+      <c r="E12" s="8">
         <v>166.37</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="8">
         <v>168.89</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="8">
         <v>2.52</v>
       </c>
     </row>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="27">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Чайка</t>
   </si>
   <si>
@@ -62,6 +68,15 @@
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>13:18</t>
+  </si>
+  <si>
+    <t>11:41</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ЗООПАРК-СЦ ВАРНА</t>
@@ -481,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -494,10 +509,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -531,22 +548,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46177</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F2">
         <v>42.95</v>
@@ -563,25 +586,31 @@
       <c r="J2">
         <v>31.78</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2">
         <v>380</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>107486</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46177</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F3">
         <v>10</v>
@@ -598,25 +627,31 @@
       <c r="J3">
         <v>15.7</v>
       </c>
-      <c r="K3">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="K3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3">
+        <v>36242</v>
+      </c>
+      <c r="M3">
+        <v>107489</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46185</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F4">
         <v>16.4</v>
@@ -633,13 +668,19 @@
       <c r="J4">
         <v>11.15</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4">
         <v>484</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="M4">
+        <v>111812</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -647,18 +688,18 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:13">
       <c r="A8" s="5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>7</v>
@@ -667,9 +708,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:13">
       <c r="A9" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" s="7">
         <v>59.35</v>
@@ -687,9 +728,9 @@
         <v>42.93</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B10" s="7">
         <v>10</v>
@@ -707,9 +748,9 @@
         <v>15.7</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="A11" s="9" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B11" s="10">
         <v>69.34999999999999</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,7 +55,10 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1199 Varna Car Osvoboditel</t>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>Варна</t>
   </si>
   <si>
     <t>ТубаЗОО</t>
@@ -76,22 +76,13 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>DIESEL DOUBLE FILTERED</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>12:07:00</t>
-  </si>
-  <si>
-    <t>09:02:00</t>
-  </si>
-  <si>
-    <t>3233492066 3233492066</t>
-  </si>
-  <si>
-    <t>3233950918 3233950918</t>
+    <t>DIESEL DOUBLE FILTER</t>
+  </si>
+  <si>
+    <t>12:07</t>
+  </si>
+  <si>
+    <t>09:02</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ЗООПАРК-СЦ ВАРНА</t>
@@ -511,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -520,17 +511,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -570,16 +560,13 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46190</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
@@ -593,32 +580,29 @@
       <c r="F2">
         <v>9.050000000000001</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H2">
+        <v>13.76</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J2">
+        <v>14.03</v>
+      </c>
+      <c r="K2" t="s">
         <v>21</v>
       </c>
-      <c r="H2">
-        <v>1.52</v>
-      </c>
-      <c r="I2" s="1">
-        <v>13.76</v>
-      </c>
-      <c r="J2">
-        <v>1.55</v>
-      </c>
-      <c r="K2" s="1">
-        <v>14.03</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
+      <c r="L2">
+        <v>180722</v>
       </c>
       <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>24</v>
+        <v>276001</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46199</v>
       </c>
@@ -637,34 +621,31 @@
       <c r="F3">
         <v>69.48999999999999</v>
       </c>
-      <c r="G3" t="s">
-        <v>21</v>
+      <c r="G3" s="1">
+        <v>1.77</v>
       </c>
       <c r="H3">
-        <v>1.74</v>
+        <v>123</v>
       </c>
       <c r="I3" s="1">
-        <v>120.91</v>
+        <v>1.77</v>
       </c>
       <c r="J3">
-        <v>1.77</v>
-      </c>
-      <c r="K3" s="1">
         <v>123</v>
       </c>
-      <c r="L3" t="s">
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3">
+        <v>141775</v>
+      </c>
+      <c r="M3">
+        <v>278473</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="M3">
-        <v>141775</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -672,27 +653,27 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:13">
       <c r="A7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>30</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:13">
       <c r="A8" s="6" t="s">
         <v>20</v>
       </c>
@@ -703,16 +684,16 @@
         <v>1</v>
       </c>
       <c r="D8" s="8">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="E8" s="7">
-        <v>120.91</v>
+        <v>123</v>
       </c>
       <c r="F8" s="7">
         <v>123</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:13">
       <c r="A9" s="6" t="s">
         <v>19</v>
       </c>
@@ -732,9 +713,9 @@
         <v>14.03</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:13">
       <c r="A10" s="9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B10" s="10">
         <v>78.54000000000001</v>
@@ -744,7 +725,7 @@
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="10">
-        <v>134.67</v>
+        <v>136.76</v>
       </c>
       <c r="F10" s="10">
         <v>137.03</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,7 +55,13 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Чайка</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
   </si>
   <si>
     <t>В1160ХМ</t>
@@ -64,7 +73,19 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-07-10 13:51:44</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>11:11:00</t>
+  </si>
+  <si>
+    <t>11:15:00</t>
+  </si>
+  <si>
+    <t>3235183545 3235183545</t>
+  </si>
+  <si>
+    <t>3235476498 3235476498</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ЗООПАРК-СЦ ВАРНА</t>
@@ -484,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -493,15 +514,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -538,116 +561,172 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46213</v>
+        <v>46225</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>17.08</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2">
+        <v>0.63</v>
+      </c>
+      <c r="I2" s="1">
+        <v>10.76</v>
+      </c>
+      <c r="J2">
+        <v>0.64</v>
+      </c>
+      <c r="K2" s="1">
+        <v>10.93</v>
+      </c>
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2">
+        <v>880</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="F2">
-        <v>26.48</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H2">
-        <v>16.42</v>
-      </c>
-      <c r="I2" s="1">
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>9.81</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3">
         <v>0.63</v>
       </c>
-      <c r="J2">
-        <v>16.68</v>
-      </c>
-      <c r="K2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L2">
-        <v>770</v>
+      <c r="I3" s="1">
+        <v>6.18</v>
+      </c>
+      <c r="J3">
+        <v>0.64</v>
+      </c>
+      <c r="K3" s="1">
+        <v>6.28</v>
+      </c>
+      <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3">
+        <v>980</v>
+      </c>
+      <c r="N3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+    <row r="6" spans="1:14">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
     </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="5" t="s">
+    <row r="7" spans="1:14">
+      <c r="A7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>9</v>
+      <c r="B8" s="7">
+        <v>26.89</v>
+      </c>
+      <c r="C8" s="7">
+        <v>2</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.63</v>
+      </c>
+      <c r="E8" s="7">
+        <v>16.94</v>
+      </c>
+      <c r="F8" s="7">
+        <v>17.21</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
-      <c r="A7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="7">
-        <v>26.48</v>
-      </c>
-      <c r="C7" s="7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8">
-        <v>0.6201</v>
-      </c>
-      <c r="E7" s="7">
-        <v>16.42</v>
-      </c>
-      <c r="F7" s="7">
-        <v>16.68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="10">
-        <v>26.48</v>
-      </c>
-      <c r="C8" s="10">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="10">
-        <v>16.42</v>
-      </c>
-      <c r="F8" s="10">
-        <v>16.68</v>
+    <row r="9" spans="1:14">
+      <c r="A9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="10">
+        <v>26.89</v>
+      </c>
+      <c r="C9" s="10">
+        <v>2</v>
+      </c>
+      <c r="D9" s="8"/>
+      <c r="E9" s="10">
+        <v>16.94</v>
+      </c>
+      <c r="F9" s="10">
+        <v>17.21</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
@@ -113,7 +113,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -697,7 +697,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="8">
-        <v>0.63</v>
+        <v>0.629974</v>
       </c>
       <c r="E8" s="7">
         <v>16.94</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -505,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -518,13 +521,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -567,98 +570,107 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46225</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>17.08</v>
+        <v>17.078</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
         <v>0.63</v>
       </c>
-      <c r="I2" s="1">
-        <v>10.76</v>
-      </c>
       <c r="J2">
+        <v>10.75914</v>
+      </c>
+      <c r="K2" s="1">
         <v>0.64</v>
       </c>
-      <c r="K2" s="1">
-        <v>10.93</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>10.92992</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2">
         <v>880</v>
       </c>
-      <c r="N2" t="s">
-        <v>22</v>
+      <c r="O2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46231</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>9.81</v>
+        <v>9.813000000000001</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1">
         <v>0.63</v>
       </c>
-      <c r="I3" s="1">
-        <v>6.18</v>
-      </c>
       <c r="J3">
+        <v>6.18219</v>
+      </c>
+      <c r="K3" s="1">
         <v>0.64</v>
       </c>
-      <c r="K3" s="1">
-        <v>6.28</v>
-      </c>
-      <c r="L3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="1">
+        <v>6.28032</v>
+      </c>
+      <c r="M3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3">
         <v>980</v>
       </c>
-      <c r="N3" t="s">
-        <v>23</v>
+      <c r="O3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="A6" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -666,38 +678,38 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="7">
-        <v>26.89</v>
+        <v>26.891</v>
       </c>
       <c r="C8" s="7">
         <v>2</v>
       </c>
       <c r="D8" s="8">
-        <v>0.629974</v>
+        <v>0.63</v>
       </c>
       <c r="E8" s="7">
         <v>16.94</v>
@@ -706,12 +718,12 @@
         <v>17.21</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="10">
-        <v>26.89</v>
+        <v>26.891</v>
       </c>
       <c r="C9" s="10">
         <v>2</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -114,9 +111,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -210,10 +207,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -521,13 +518,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -570,107 +567,98 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46225</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
       </c>
       <c r="F2">
         <v>17.078</v>
       </c>
       <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2">
+        <v>0.63</v>
+      </c>
+      <c r="I2" s="1">
+        <v>10.759</v>
+      </c>
+      <c r="J2">
+        <v>0.64</v>
+      </c>
+      <c r="K2" s="1">
+        <v>10.93</v>
+      </c>
+      <c r="L2" t="s">
         <v>20</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J2">
-        <v>10.75914</v>
-      </c>
-      <c r="K2" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L2" s="1">
-        <v>10.92992</v>
-      </c>
-      <c r="M2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>880</v>
       </c>
-      <c r="O2" t="s">
-        <v>23</v>
+      <c r="N2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46231</v>
       </c>
       <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
       </c>
       <c r="F3">
         <v>9.813000000000001</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="I3" s="1">
-        <v>0.63</v>
+        <v>6.182</v>
       </c>
       <c r="J3">
-        <v>6.18219</v>
+        <v>0.64</v>
       </c>
       <c r="K3" s="1">
-        <v>0.64</v>
-      </c>
-      <c r="L3" s="1">
-        <v>6.28032</v>
-      </c>
-      <c r="M3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3">
+        <v>6.28</v>
+      </c>
+      <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3">
         <v>980</v>
       </c>
-      <c r="O3" t="s">
+      <c r="N3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="4" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -678,49 +666,49 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:14">
       <c r="A7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14">
       <c r="A8" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="7">
         <v>26.891</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <v>2</v>
       </c>
       <c r="D8" s="8">
         <v>0.63</v>
       </c>
-      <c r="E8" s="7">
-        <v>16.94</v>
-      </c>
-      <c r="F8" s="7">
+      <c r="E8" s="8">
+        <v>16.941</v>
+      </c>
+      <c r="F8" s="8">
         <v>17.21</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="10">
         <v>26.891</v>
@@ -730,7 +718,7 @@
       </c>
       <c r="D9" s="8"/>
       <c r="E9" s="10">
-        <v>16.94</v>
+        <v>16.941</v>
       </c>
       <c r="F9" s="10">
         <v>17.21</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,34 +55,34 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1158 Варна Чайка</t>
-  </si>
-  <si>
-    <t>1148 Варна пристанище</t>
+    <t>Варна Чайка</t>
+  </si>
+  <si>
+    <t>Варна Цар Освободител</t>
+  </si>
+  <si>
+    <t>ТубаЗОО</t>
   </si>
   <si>
     <t>В1160ХМ</t>
   </si>
   <si>
+    <t>78970155027722788</t>
+  </si>
+  <si>
     <t>78970155027722754</t>
   </si>
   <si>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>11:11:00</t>
-  </si>
-  <si>
-    <t>11:15:00</t>
-  </si>
-  <si>
-    <t>3235183545 3235183545</t>
-  </si>
-  <si>
-    <t>3235476498 3235476498</t>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>10:30</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ЗООПАРК-СЦ ВАРНА</t>
@@ -111,9 +108,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -207,10 +204,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -505,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -514,17 +511,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -564,101 +560,92 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46225</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
         <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>17.078</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
+        <v>10</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.52</v>
       </c>
       <c r="H2">
-        <v>0.63</v>
+        <v>15.2</v>
       </c>
       <c r="I2" s="1">
-        <v>10.759</v>
+        <v>1.55</v>
       </c>
       <c r="J2">
-        <v>0.64</v>
-      </c>
-      <c r="K2" s="1">
-        <v>10.93</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
+        <v>15.5</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>880</v>
-      </c>
-      <c r="N2" t="s">
-        <v>22</v>
+        <v>140555</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
-        <v>46231</v>
+        <v>46238</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3">
-        <v>9.813000000000001</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
+        <v>15.727</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.65</v>
       </c>
       <c r="H3">
-        <v>0.63</v>
+        <v>10.223</v>
       </c>
       <c r="I3" s="1">
-        <v>6.182</v>
+        <v>0.66</v>
       </c>
       <c r="J3">
-        <v>0.64</v>
-      </c>
-      <c r="K3" s="1">
-        <v>6.28</v>
-      </c>
-      <c r="L3" t="s">
-        <v>21</v>
+        <v>10.38</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3">
+        <v>1080</v>
       </c>
       <c r="M3">
-        <v>980</v>
-      </c>
-      <c r="N3" t="s">
+        <v>289344</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="4" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -666,62 +653,82 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:13">
       <c r="A7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="7">
+        <v>15.727</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1</v>
+      </c>
+      <c r="D8" s="8">
+        <v>0.65003</v>
+      </c>
+      <c r="E8" s="7">
+        <v>10.22</v>
+      </c>
+      <c r="F8" s="7">
+        <v>10.38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="7">
+        <v>10</v>
+      </c>
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1.52</v>
+      </c>
+      <c r="E9" s="7">
+        <v>15.2</v>
+      </c>
+      <c r="F9" s="7">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="7">
-        <v>26.891</v>
-      </c>
-      <c r="C8" s="8">
+      <c r="B10" s="10">
+        <v>25.727</v>
+      </c>
+      <c r="C10" s="10">
         <v>2</v>
       </c>
-      <c r="D8" s="8">
-        <v>0.63</v>
-      </c>
-      <c r="E8" s="8">
-        <v>16.941</v>
-      </c>
-      <c r="F8" s="8">
-        <v>17.21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="10">
-        <v>26.891</v>
-      </c>
-      <c r="C9" s="10">
-        <v>2</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="10">
-        <v>16.941</v>
-      </c>
-      <c r="F9" s="10">
-        <v>17.21</v>
+      <c r="D10" s="8"/>
+      <c r="E10" s="10">
+        <v>25.42</v>
+      </c>
+      <c r="F10" s="10">
+        <v>25.88</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="40">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,34 +58,64 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>Варна Цар Освободител</t>
+    <t>1158 Варна Чайка</t>
+  </si>
+  <si>
+    <t>В1160ХМ</t>
+  </si>
+  <si>
+    <t>B4126CH</t>
   </si>
   <si>
     <t>ТубаЗОО</t>
   </si>
   <si>
-    <t>В1160ХМ</t>
+    <t>78970155027722754</t>
+  </si>
+  <si>
+    <t>78970155027720584</t>
   </si>
   <si>
     <t>78970155027722788</t>
   </si>
   <si>
-    <t>78970155027722754</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>10:30</t>
+    <t>DIESEL EKONOMY</t>
+  </si>
+  <si>
+    <t>DIESEL DOUBLE FILTERED</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>13:35:00</t>
+  </si>
+  <si>
+    <t>13:36:00</t>
+  </si>
+  <si>
+    <t>12:06:00</t>
+  </si>
+  <si>
+    <t>10:53:00</t>
+  </si>
+  <si>
+    <t>3236916182 3236916182</t>
+  </si>
+  <si>
+    <t>3236917515 3236917515</t>
+  </si>
+  <si>
+    <t>3236929082 3236929082</t>
+  </si>
+  <si>
+    <t>3237207096 3237207096</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ЗООПАРК-СЦ ВАРНА</t>
@@ -107,10 +140,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -190,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -204,10 +238,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -502,7 +538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -511,16 +547,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -560,180 +597,317 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46237</v>
+        <v>46259</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F2">
         <v>10</v>
       </c>
-      <c r="G2" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H2">
-        <v>15.2</v>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1.459</v>
       </c>
       <c r="I2" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J2">
-        <v>15.5</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
+        <v>14.59</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1.58</v>
+      </c>
+      <c r="K2" s="1">
+        <v>15.8</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
       </c>
       <c r="M2">
-        <v>140555</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>1280</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
-        <v>46238</v>
+        <v>46259</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
         <v>18</v>
       </c>
       <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3">
+        <v>26.8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I3" s="1">
+        <v>26.532</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K3" s="1">
+        <v>17.688</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3">
+        <v>1280</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4">
+        <v>46.95</v>
+      </c>
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1.719</v>
+      </c>
+      <c r="I4" s="1">
+        <v>80.70699999999999</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1.85</v>
+      </c>
+      <c r="K4" s="1">
+        <v>86.858</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4">
+        <v>142230</v>
+      </c>
+      <c r="N4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3">
+        <v>46265</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="F3">
-        <v>15.727</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H3">
-        <v>10.223</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J3">
-        <v>10.38</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5">
+        <v>10.03</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="1">
+        <v>1.819</v>
+      </c>
+      <c r="I5" s="1">
+        <v>18.245</v>
+      </c>
+      <c r="J5" s="1">
+        <v>2.1</v>
+      </c>
+      <c r="K5" s="1">
+        <v>21.063</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="7">
+        <v>46.95</v>
+      </c>
+      <c r="C10" s="8">
+        <v>1</v>
+      </c>
+      <c r="D10" s="9">
+        <v>1.719</v>
+      </c>
+      <c r="E10" s="7">
+        <v>80.70999999999999</v>
+      </c>
+      <c r="F10" s="7">
+        <v>86.86</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L3">
-        <v>1080</v>
-      </c>
-      <c r="M3">
-        <v>289344</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="5" t="s">
+      <c r="B11" s="7">
+        <v>26.8</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9">
+        <v>0.99</v>
+      </c>
+      <c r="E11" s="7">
+        <v>26.53</v>
+      </c>
+      <c r="F11" s="7">
+        <v>17.69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="7">
-        <v>15.727</v>
-      </c>
-      <c r="C8" s="7">
+      <c r="B12" s="7">
+        <v>10.03</v>
+      </c>
+      <c r="C12" s="8">
         <v>1</v>
       </c>
-      <c r="D8" s="8">
-        <v>0.65003</v>
-      </c>
-      <c r="E8" s="7">
-        <v>10.22</v>
-      </c>
-      <c r="F8" s="7">
-        <v>10.38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="7">
+      <c r="D12" s="9">
+        <v>1.81904</v>
+      </c>
+      <c r="E12" s="7">
+        <v>18.24</v>
+      </c>
+      <c r="F12" s="7">
+        <v>21.06</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="7">
         <v>10</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C13" s="8">
         <v>1</v>
       </c>
-      <c r="D9" s="8">
-        <v>1.52</v>
-      </c>
-      <c r="E9" s="7">
-        <v>15.2</v>
-      </c>
-      <c r="F9" s="7">
-        <v>15.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="10">
-        <v>25.727</v>
-      </c>
-      <c r="C10" s="10">
-        <v>2</v>
-      </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="10">
-        <v>25.42</v>
-      </c>
-      <c r="F10" s="10">
-        <v>25.88</v>
+      <c r="D13" s="9">
+        <v>1.459</v>
+      </c>
+      <c r="E13" s="7">
+        <v>14.59</v>
+      </c>
+      <c r="F13" s="7">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="11">
+        <v>93.78</v>
+      </c>
+      <c r="C14" s="12">
+        <v>4</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="11">
+        <v>140.07</v>
+      </c>
+      <c r="F14" s="11">
+        <v>141.41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ЗООПАРК-СЦ ВАРНА/ОП ЗООПАРК-СЦ ВАРНА.xlsx
@@ -624,10 +624,10 @@
         <v>25</v>
       </c>
       <c r="H2" s="1">
-        <v>1.459</v>
+        <v>1.55</v>
       </c>
       <c r="I2" s="1">
-        <v>14.59</v>
+        <v>15.5</v>
       </c>
       <c r="J2" s="1">
         <v>1.58</v>
@@ -668,10 +668,10 @@
         <v>25</v>
       </c>
       <c r="H3" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I3" s="1">
-        <v>26.532</v>
+        <v>17.42</v>
       </c>
       <c r="J3" s="1">
         <v>0.66</v>
@@ -712,10 +712,10 @@
         <v>25</v>
       </c>
       <c r="H4" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I4" s="1">
-        <v>80.70699999999999</v>
+        <v>85.449</v>
       </c>
       <c r="J4" s="1">
         <v>1.85</v>
@@ -756,10 +756,10 @@
         <v>25</v>
       </c>
       <c r="H5" s="1">
-        <v>1.819</v>
+        <v>2.07</v>
       </c>
       <c r="I5" s="1">
-        <v>18.245</v>
+        <v>20.762</v>
       </c>
       <c r="J5" s="1">
         <v>2.1</v>
@@ -818,10 +818,10 @@
         <v>1</v>
       </c>
       <c r="D10" s="9">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="E10" s="7">
-        <v>80.70999999999999</v>
+        <v>85.45</v>
       </c>
       <c r="F10" s="7">
         <v>86.86</v>
@@ -838,10 +838,10 @@
         <v>1</v>
       </c>
       <c r="D11" s="9">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="E11" s="7">
-        <v>26.53</v>
+        <v>17.42</v>
       </c>
       <c r="F11" s="7">
         <v>17.69</v>
@@ -858,10 +858,10 @@
         <v>1</v>
       </c>
       <c r="D12" s="9">
-        <v>1.81904</v>
+        <v>2.06999</v>
       </c>
       <c r="E12" s="7">
-        <v>18.24</v>
+        <v>20.76</v>
       </c>
       <c r="F12" s="7">
         <v>21.06</v>
@@ -878,10 +878,10 @@
         <v>1</v>
       </c>
       <c r="D13" s="9">
-        <v>1.459</v>
+        <v>1.55</v>
       </c>
       <c r="E13" s="7">
-        <v>14.59</v>
+        <v>15.5</v>
       </c>
       <c r="F13" s="7">
         <v>15.8</v>
@@ -899,7 +899,7 @@
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="11">
-        <v>140.07</v>
+        <v>139.13</v>
       </c>
       <c r="F14" s="11">
         <v>141.41</v>
